--- a/output/full_scan/batch_seq8_2026-09-04.xlsx
+++ b/output/full_scan/batch_seq8_2026-09-04.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>957.2936567524756</v>
+        <v>1127.293656752475</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1930</v>
@@ -552,7 +552,7 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>60.46617889373963</v>
+        <v>60.46617889866626</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>14.51444619699437</v>
@@ -564,57 +564,57 @@
         <v>2</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>32.01565632175529</v>
+        <v>32.0156563219462</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6949</v>
+        <v>7744</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>893.8507131299439</v>
+        <v>1044.544216958605</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1490</v>
+        <v>545</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G3" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>84.44665559837873</v>
+        <v>64.88788101632923</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>38.6367393150523</v>
+        <v>36.4658440918942</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.896361293282596</v>
+        <v>1.276690242685392</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,31 +623,31 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>44.09810044693842</v>
+        <v>3.796018932328082</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>7744</v>
+        <v>6924</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>874.5442169586046</v>
+        <v>1024.283919874536</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>545</v>
+        <v>123</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
@@ -658,16 +658,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>64.88788100159334</v>
+        <v>60.04927727846536</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>36.46584406363973</v>
+        <v>20.3911340628514</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.276690242685392</v>
+        <v>1.634472132012004</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>3.796018932518905</v>
+        <v>0.6346803483953301</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>6924</v>
+        <v>7703</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>864.2839198745363</v>
+        <v>947.0096441402542</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>123</v>
+        <v>187.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,13 +711,13 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>60.04927642340075</v>
+        <v>57.19363679084842</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>20.39113406249315</v>
+        <v>10.03363993537115</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>1.634472132012004</v>
+        <v>1.971090908963831</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>0</v>
@@ -729,31 +729,31 @@
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>0.6346803483953301</v>
+        <v>1.220710832878864</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7788</v>
+        <v>7711</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>816.9451664312082</v>
+        <v>934.0281837165704</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>335</v>
+        <v>632</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>70.94668378303751</v>
+        <v>75.15705779677027</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>33.58904544752146</v>
+        <v>49.62145554531686</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.834888185877003</v>
+        <v>1.457700100063641</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>5.491372357382282</v>
+        <v>10.1425211079316</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7703</v>
+        <v>6906</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>807.0096441402541</v>
+        <v>934</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>187.5</v>
+        <v>84.3</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>57.19363687092705</v>
+        <v>66.76246569063986</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>10.03363989973387</v>
+        <v>29.00746985861029</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.971090908963831</v>
+        <v>5.14642272121203</v>
       </c>
       <c r="K7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>1.220710831924879</v>
+        <v>1.407293550786955</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6906</v>
+        <v>7788</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>794</v>
+        <v>916.9451664312082</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>84.3</v>
+        <v>335</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>66.76246579040354</v>
+        <v>70.94668379201664</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>29.00746986189556</v>
+        <v>33.58904538172867</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>5.14642272121203</v>
+        <v>1.834888185877003</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>0</v>
@@ -888,51 +888,51 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1.407293550786955</v>
+        <v>5.491372357191466</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7717</v>
+        <v>6949</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>767.8157705254544</v>
+        <v>893.8507131299439</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>449.5</v>
+        <v>1490</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>55.97726964034244</v>
+        <v>84.44665559983355</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>12.98694000798016</v>
+        <v>38.63673936851899</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>5.724560932434314</v>
+        <v>1.896361293282596</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>4.784940138851269</v>
+        <v>44.09810044677498</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6840</v>
+        <v>7717</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>759.9423723799327</v>
+        <v>882.8157705254544</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>92.8</v>
+        <v>449.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>69.25117454639032</v>
+        <v>55.97726964034244</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>39.60587043626386</v>
+        <v>12.98694000798016</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.6392750030237313</v>
+        <v>5.724560932434314</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.113161111492019</v>
+        <v>4.784940138851269</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6922</v>
+        <v>6838</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>台新藥</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>729.7862230060899</v>
+        <v>839.0249827251873</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>208.5</v>
+        <v>24.65</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,16 +1029,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>57.71339471605469</v>
+        <v>67.5653155796922</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>26.98606708743172</v>
+        <v>17.69877200553887</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.4463902118273317</v>
+        <v>2.40350461620568</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L11" s="2" t="n">
         <v>0</v>
@@ -1047,11 +1047,11 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.4299679052247338</v>
+        <v>0.1962972957710152</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>705.5804638024857</v>
+        <v>820.5804638024857</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>308</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>69.54500228384063</v>
+        <v>69.54500232453209</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>51.10176848033073</v>
@@ -1100,31 +1100,31 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>1.567833001951019</v>
+        <v>1.567833001569451</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6913</v>
+        <v>7738</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>鴻呈</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>675.1426913804323</v>
+        <v>784</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>56.15246414558245</v>
+        <v>64.49668740595513</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>28.0532743349924</v>
+        <v>34.96097428703371</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.091800348961224</v>
+        <v>5.017113442507626</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.1562150060895799</v>
+        <v>0.7452393862898536</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7738</v>
+        <v>6840</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>644</v>
+        <v>759.9423723799327</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>175</v>
+        <v>92.8</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>64.49668740595513</v>
+        <v>69.25117455125552</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>34.96097423037868</v>
+        <v>39.6058704644428</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>5.017113442507626</v>
+        <v>0.6392750030237313</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.745239386576009</v>
+        <v>0.1131611115111006</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>7810</v>
+        <v>6855</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>640.1982375237533</v>
+        <v>744.854567633653</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>217.5</v>
+        <v>120.5</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>60.17669712294525</v>
+        <v>52.42670653543669</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>36.17471126183177</v>
+        <v>10.23569172748919</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.5106865455310544</v>
+        <v>0.1953490494990757</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.134384297725407</v>
+        <v>1.586724078854628</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7711</v>
+        <v>7772</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>624.0281837165703</v>
+        <v>742.3345617114879</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>632</v>
+        <v>109</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>75.15705774883861</v>
+        <v>66.96896989915876</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>49.62145553616001</v>
+        <v>17.24842643524097</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.457700100063641</v>
+        <v>1.700468758625462</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>10.14252110955334</v>
+        <v>2.769843634840778</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>7795</v>
+        <v>6859</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>608.0918141617951</v>
+        <v>736.9164063803244</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>505</v>
+        <v>115</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>49.070992440277</v>
+        <v>61.11903421140968</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>20.03369673437944</v>
+        <v>24.79742322012929</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.7673253930595313</v>
+        <v>0.5407812501425823</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>-8.154720801481012</v>
+        <v>0.8638555831185161</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7631</v>
+        <v>6922</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>605.2624664404711</v>
+        <v>729.7862230060899</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>146</v>
+        <v>208.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,16 +1400,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>54.38616443277274</v>
+        <v>57.71339476319737</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>24.79786957447612</v>
+        <v>26.98606712072698</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.6731219906572913</v>
+        <v>0.4463902118273317</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>-0.1957008087388521</v>
+        <v>-0.4299679060833039</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6855</v>
+        <v>7750</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>604.854567633653</v>
+        <v>729.2018146985049</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>120.5</v>
+        <v>2415</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,49 +1453,49 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>52.42670653308444</v>
+        <v>54.83113653150895</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>10.23569172627577</v>
+        <v>12.32004331495105</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.1953490494990757</v>
+        <v>0.8330266798729018</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>1.586724079045426</v>
+        <v>-13.35600366872475</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7712</v>
+        <v>6885</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>591.1260259686482</v>
+        <v>727.6253351830812</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>155</v>
+        <v>24.1</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>54.04239353679512</v>
+        <v>66.31338851554113</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>19.40525068865822</v>
+        <v>38.21285609003619</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.386259881957777</v>
+        <v>1.229289981417772</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.197363274203271</v>
+        <v>0.3353797560711619</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>7750</v>
+        <v>6870</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>589.2018146985052</v>
+        <v>722.6508768955487</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2415</v>
+        <v>290</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>54.83113650502904</v>
+        <v>63.06191213690037</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>12.32004313290148</v>
+        <v>15.15495934087058</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.8330266798729018</v>
+        <v>0.8631298069376864</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-13.35600366261944</v>
+        <v>4.246859288517019</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6918</v>
+        <v>7631</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>585.3116585964341</v>
+        <v>720.2624664404711</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>77.8</v>
+        <v>146</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,16 +1612,16 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>63.70529715742049</v>
+        <v>54.38616440498283</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>40.12428366355782</v>
+        <v>24.79786960864775</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.425486562922303</v>
+        <v>0.6731219906572913</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.2629776840784141</v>
+        <v>-0.1957008085480407</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6859</v>
+        <v>6913</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>鴻呈</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>566.9164063803244</v>
+        <v>675.1426913804323</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>61.119034120826</v>
+        <v>56.15246419623298</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>24.79742321740192</v>
+        <v>28.05327437904259</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5407812501425823</v>
+        <v>1.091800348961224</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.8638555835001063</v>
+        <v>-0.1562150064711573</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6838</v>
+        <v>6887</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>台新藥</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>559.0249827251874</v>
+        <v>652.2525065968031</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>24.65</v>
+        <v>38.05</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>67.56531543713706</v>
+        <v>54.09055280979389</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>17.69877191733033</v>
+        <v>28.19666617359609</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2.40350461620568</v>
+        <v>0.4156025268190911</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.1962972958759533</v>
+        <v>0.0341248339264749</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6885</v>
+        <v>6894</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>557.6253351830811</v>
+        <v>645.2693825509793</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>24.1</v>
+        <v>353</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>66.31338850902452</v>
+        <v>57.60088866812838</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>38.21285604430364</v>
+        <v>16.84468606005593</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.229289981417772</v>
+        <v>0.4902491735150761</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.3353797561570204</v>
+        <v>2.660558627586624</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>7772</v>
+        <v>6996</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>542.3345617114879</v>
+        <v>641.0483277769138</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>109</v>
+        <v>183.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>66.96896985056617</v>
+        <v>55.7065448047017</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>17.24842635876823</v>
+        <v>12.38825578067636</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.700468758625462</v>
+        <v>0.7072508966568415</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>2.769843636119097</v>
+        <v>0.7525490645484952</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6887</v>
+        <v>7810</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>542.2525065968031</v>
+        <v>640.1982375237531</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>38.05</v>
+        <v>217.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>54.09055281586553</v>
+        <v>60.17669699503395</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>28.1966661459597</v>
+        <v>36.17471117178224</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.4156025268190911</v>
+        <v>0.5106865455310544</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.0341248340981906</v>
+        <v>1.134384298965584</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>7556</v>
+        <v>6983</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>541.4217198607799</v>
+        <v>636.384630318318</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>248.5</v>
+        <v>355</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>52.9187050232791</v>
+        <v>63.00362281533317</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>27.03929789481385</v>
+        <v>22.15974542844675</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.341494023978346</v>
+        <v>0.8783758447981859</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>0.1582844768033702</v>
+        <v>7.127577467411858</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6894</v>
+        <v>6952</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>530.2693825509793</v>
+        <v>626.4856131848043</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>353</v>
+        <v>38.2</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>57.6008886632962</v>
+        <v>52.3292023488763</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>16.84468606005593</v>
+        <v>20.65304917316739</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.4902491735150761</v>
+        <v>0.787958927339705</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>1</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>2.660558627872843</v>
+        <v>-1.419072455332676</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6870</v>
+        <v>6962</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>522.6508768955487</v>
+        <v>604.0207867148856</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>290</v>
+        <v>31.95</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>63.0619121277376</v>
+        <v>49.2517457313813</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15.15495935854836</v>
+        <v>15.88143557356245</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.8631298069376864</v>
+        <v>0.3936055547100562</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>4.246859288803202</v>
+        <v>0.2073942254572092</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, bb_squeeze_breakout, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6983</v>
+        <v>7610</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>521.3846303183205</v>
+        <v>602.8400491477936</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>355</v>
+        <v>1820</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>63.00362354659618</v>
+        <v>55.46601201435142</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>22.1597454263269</v>
+        <v>12.41334242323964</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.8783758447981859</v>
+        <v>0.6750722681083622</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>7.127577467698085</v>
+        <v>18.64057021154239</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6952</v>
+        <v>6936</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>511.485613184804</v>
+        <v>601.2465200699711</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>38.2</v>
+        <v>32.8</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>52.32920234800479</v>
+        <v>56.85879762148729</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>20.65304913908444</v>
+        <v>37.44328519132071</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.787958927339705</v>
+        <v>0.4838120873852596</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-1.419072455323138</v>
+        <v>0.0500460429114688</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, williams_r_recovery, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6953</v>
+        <v>7795</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>510.4890815898837</v>
+        <v>598.0918141617951</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>238.5</v>
+        <v>505</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>56.28360969938515</v>
+        <v>49.070992440277</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>19.68803582415347</v>
+        <v>20.03369673437944</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.5099861391129032</v>
+        <v>0.7673253930595313</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>1.076665761636644</v>
+        <v>-8.154720801385583</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>7714</v>
+        <v>7712</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>506.6737276544986</v>
+        <v>591.1260259686482</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>160.5</v>
+        <v>155</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>46.57049096181109</v>
+        <v>54.04239359307444</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>22.00663485691416</v>
+        <v>19.40525072048541</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.2317437986334909</v>
+        <v>0.386259881957777</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>-1.767438927215818</v>
+        <v>1.197363273726242</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6996</v>
+        <v>6918</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>501.0483277769131</v>
+        <v>585.3116585964345</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>183.5</v>
+        <v>77.8</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>55.70654476882198</v>
+        <v>63.70529741823092</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>12.38825567950228</v>
+        <v>40.12428373453698</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.7072508966568415</v>
+        <v>1.425486562922303</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.7525490650254717</v>
+        <v>0.2629776834106425</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6936</v>
+        <v>7689</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>486.246520069971</v>
+        <v>581.4653716463422</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>32.8</v>
+        <v>172.5</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>56.85879758115188</v>
+        <v>37.74184341176232</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>37.44328510405112</v>
+        <v>21.49558839667703</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.4838120873852596</v>
+        <v>0.4982185900452315</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>0.0500460429400909</v>
+        <v>1.512085250009332</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6969</v>
+        <v>6895</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>477.0003325116118</v>
+        <v>560.0234636998812</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>33.4</v>
+        <v>156.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>50.77105633242276</v>
+        <v>65.06933304580556</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>21.32112022553561</v>
+        <v>31.83443493308168</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.4893449776611547</v>
+        <v>0.5981010782634625</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.2769651926363183</v>
+        <v>3.18526434825591</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7689</v>
+        <v>7730</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>471.4653716463421</v>
+        <v>555.9575366345416</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>172.5</v>
+        <v>186.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>37.74184341176232</v>
+        <v>59.67576585885918</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>21.49558839667703</v>
+        <v>17.09983417588636</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.4982185900452315</v>
+        <v>2.074341994116879</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1.512085250009332</v>
+        <v>1.73047231896998</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>7728</v>
+        <v>7556</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>465.7809519997748</v>
+        <v>541.4217198607799</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>618</v>
+        <v>248.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>49.84997195201419</v>
+        <v>52.9187050232791</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>21.82012839710688</v>
+        <v>27.03929788185729</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.883297010338083</v>
+        <v>0.341494023978346</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>6.178711763092378</v>
+        <v>0.1582844775665526</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6937</v>
+        <v>6928</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>452.6259814491402</v>
+        <v>534.581167894229</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>283</v>
+        <v>48.5</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>53.43522917371648</v>
+        <v>49.62300734836113</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>12.60142001150858</v>
+        <v>13.05450762146553</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.10379716594245</v>
+        <v>0.7419145607072704</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.315599016106546</v>
+        <v>0.1423870366926409</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7768</v>
+        <v>6953</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>446.630523987551</v>
+        <v>510.489081589884</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>282.5</v>
+        <v>238.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>47.97172920646241</v>
+        <v>56.28360969374813</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>20.04553340551234</v>
+        <v>19.68803588294917</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.9199192138392864</v>
+        <v>0.5099861391129032</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.273873202942327</v>
+        <v>1.076665761255085</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>8039</v>
+        <v>7714</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>436.4314601937541</v>
+        <v>506.6737276544986</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>297.5</v>
+        <v>160.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>56.87060083590895</v>
+        <v>46.57049097564811</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>36.39745644667496</v>
+        <v>22.00663485868231</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.007033224007395</v>
+        <v>0.2317437986334909</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>-2.656257741960253</v>
+        <v>-1.767438927864518</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6903</v>
+        <v>7822</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>427.761547922031</v>
+        <v>496.4118746234848</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>312.5</v>
+        <v>922</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45.55163847355536</v>
+        <v>51.30843696148444</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>14.03627480460148</v>
+        <v>10.96239487349763</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.7171207402894895</v>
+        <v>0.5277602777635327</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>1.69702706652372</v>
+        <v>3.701501831117731</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7751</v>
+        <v>6916</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>423.0597979048521</v>
+        <v>484.4184158452994</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1610</v>
+        <v>18.7</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,49 +2778,49 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>52.76010606633578</v>
+        <v>50.32579262827253</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>17.54897827624739</v>
+        <v>8.421526717857873</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.6124866307765134</v>
+        <v>0.8810027689632582</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-20.03017047802027</v>
+        <v>0.0406695324393583</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>7822</v>
+        <v>6969</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>421.4118746234848</v>
+        <v>477.0003325116118</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>922</v>
+        <v>33.4</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>51.30843692641713</v>
+        <v>50.771056353011</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>10.96239476797851</v>
+        <v>21.32112006094933</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5277602777635327</v>
+        <v>0.4893449776611547</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>3.70150183483821</v>
+        <v>-0.2769651926267791</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6895</v>
+        <v>6861</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>420.0234636998804</v>
+        <v>469.4732056392171</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>156.5</v>
+        <v>183</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>65.06933289065279</v>
+        <v>37.34721155417302</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>31.83443492226866</v>
+        <v>23.01887412611561</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.5981010782634625</v>
+        <v>0.700661562679507</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>3.185264350068476</v>
+        <v>1.233465681915956</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7730</v>
+        <v>7728</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>415.9575366345415</v>
+        <v>465.7809519997752</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>186.5</v>
+        <v>618</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>59.67576594857198</v>
+        <v>49.84997198621699</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>17.09983412098316</v>
+        <v>21.8201284358654</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.074341994116879</v>
+        <v>1.883297010338083</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1.730472316966626</v>
+        <v>6.17871176213856</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>8021</v>
+        <v>7769</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>414.9235794178253</v>
+        <v>447.4755334582267</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>420</v>
+        <v>5980</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>49.27801129134048</v>
+        <v>44.40543383252964</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>11.05955062179931</v>
+        <v>10.2938620462295</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.06353327170635</v>
+        <v>0.6716804827323589</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>3.215488415406311</v>
+        <v>-56.4157649734309</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6907</v>
+        <v>7768</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>404.5220664284296</v>
+        <v>446.630523987551</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>181.5</v>
+        <v>282.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>48.72072232847035</v>
+        <v>47.97172922888675</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>14.09155754237571</v>
+        <v>20.04553327505847</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.3389409795935543</v>
+        <v>0.9199192138392864</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.6086672557274233</v>
+        <v>1.27387320246534</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6944</v>
+        <v>6937</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>401.6179812147515</v>
+        <v>442.6259814491401</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>696</v>
+        <v>283</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>36.19890297706787</v>
+        <v>53.43522923237629</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>26.84451850565029</v>
+        <v>12.60142000875602</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.266648826227605</v>
+        <v>1.10379716594245</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>4.367929759766461</v>
+        <v>1.31559901467554</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>8016</v>
+        <v>6854</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>401.2882494594394</v>
+        <v>436.9344592231602</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>293.5</v>
+        <v>92.8</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>48.34913200341926</v>
+        <v>45.60685651074743</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>8.762403633045279</v>
+        <v>20.15794628747116</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.2921757745138847</v>
+        <v>1.406490578488159</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.3732644851680591</v>
+        <v>1.068280012730306</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>7715</v>
+        <v>8039</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>396.306156724028</v>
+        <v>436.4314601937541</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>28.95</v>
+        <v>297.5</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,49 +3202,49 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>36.64180604558674</v>
+        <v>56.87060083414528</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>21.91574562828202</v>
+        <v>36.39745645879732</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.4173106929447723</v>
+        <v>1.007033224007395</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M52" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.2130940360015711</v>
+        <v>-2.656257741559564</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6865</v>
+        <v>6903</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>394.5293119943663</v>
+        <v>427.761547922031</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>25.55</v>
+        <v>312.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>53.13600533989449</v>
+        <v>45.55163847355536</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>9.983006608708251</v>
+        <v>14.03627480889082</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.245544017358958</v>
+        <v>0.7171207402894895</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.6626598463978152</v>
+        <v>1.69702706652372</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>7823</v>
+        <v>7780</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>391.0802875326286</v>
+        <v>427.7073091758221</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>83</v>
+        <v>16.7</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,49 +3308,49 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>47.44145936649989</v>
+        <v>44.12320168534662</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>21.35354095074747</v>
+        <v>16.81769296208022</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.384836320499791</v>
+        <v>0.7757530566864309</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M54" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>-0.0640491053983417</v>
+        <v>0.0236785816856596</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, invest_trust_buy_2d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6931</v>
+        <v>7751</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>391.0483452888826</v>
+        <v>423.0597979048521</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>41</v>
+        <v>1610</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,49 +3361,49 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>52.4970574074726</v>
+        <v>52.76010606828741</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>26.39830812199078</v>
+        <v>17.54897827624739</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.4811506373813949</v>
+        <v>0.6124866307765134</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-0.1023227276510604</v>
+        <v>-20.03017047821091</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>7805</v>
+        <v>6908</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>380.6312236449497</v>
+        <v>417.7246661242642</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>508</v>
+        <v>30.1</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>30.86769538692924</v>
+        <v>32.04585721622632</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>37.70693087859446</v>
+        <v>32.46986331686183</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.3052466258249975</v>
+        <v>2.175538576576189</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-10.25911596235908</v>
+        <v>0.082080522347431</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>7402</v>
+        <v>8021</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>379.7795465164086</v>
+        <v>414.9235794178257</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>104.5</v>
+        <v>420</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>45.00936178671891</v>
+        <v>49.27801129317864</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>19.37698361208553</v>
+        <v>11.059550643844</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.2839218473967748</v>
+        <v>1.06353327170635</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.4155022184138763</v>
+        <v>3.215488415272788</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7842</v>
+        <v>7855</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>379.6098523560556</v>
+        <v>408.8676084869969</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>98.2</v>
+        <v>42.75</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>52.1773657586829</v>
+        <v>17.80758267521959</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>16.99644001272341</v>
+        <v>50.6962449920645</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.2475735057081269</v>
+        <v>0.2899570422745821</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.3664131889385227</v>
+        <v>1.608708396311524</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>7820</v>
+        <v>6907</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>369.1871962403344</v>
+        <v>404.5220664284296</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>118</v>
+        <v>181.5</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>51.04015041709878</v>
+        <v>48.72072232847035</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>17.36585694009663</v>
+        <v>14.09155754237571</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2.021117603816445</v>
+        <v>0.3389409795935543</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-0.4054582952090002</v>
+        <v>-0.6086672557274233</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6965</v>
+        <v>6944</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>363.8039266829342</v>
+        <v>401.6179812147515</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>73.8</v>
+        <v>696</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,49 +3626,49 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>39.45543300841008</v>
+        <v>36.19890304898755</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>37.10149796386691</v>
+        <v>26.84451863735854</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.4990695581588331</v>
+        <v>1.266648826227605</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.0027468199285454</v>
+        <v>4.367929755568994</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6863</v>
+        <v>6994</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>363.6216242821312</v>
+        <v>401.3529453072314</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>104.5</v>
+        <v>35.2</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>37.33017903838645</v>
+        <v>37.8425842150076</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>16.41709100148537</v>
+        <v>28.10109158338954</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.4657062153519374</v>
+        <v>0.9523016077320916</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-1.200410794378826</v>
+        <v>0.3058752975511156</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6957</v>
+        <v>8016</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>363.5223086752743</v>
+        <v>401.2882494594394</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>219.5</v>
+        <v>293.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>51.34309112911537</v>
+        <v>48.34913201942131</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>13.83856066849919</v>
+        <v>8.762403700219322</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.7229410612273673</v>
+        <v>0.2921757745138847</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.072493383827203</v>
+        <v>-0.3732644854542002</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6877</v>
+        <v>7715</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>359.7024639874857</v>
+        <v>396.306156724028</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>110.5</v>
+        <v>28.95</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>37.74654032330565</v>
+        <v>36.64180613232024</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>22.39606341909924</v>
+        <v>21.91574567124181</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.6390365203270036</v>
+        <v>0.4173106929447723</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.4747157696942912</v>
+        <v>-0.2130940360492653</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6951</v>
+        <v>7721</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>359.6187154235273</v>
+        <v>395.2535410459928</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>71</v>
+        <v>60.9</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>38.79163094884583</v>
+        <v>43.33639311374811</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>23.75265980203528</v>
+        <v>14.341506651236</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2.49452417335253</v>
+        <v>0.6352258708211707</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1006438858429181</v>
+        <v>0.092855874810336</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6962</v>
+        <v>6865</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>354.0207867148857</v>
+        <v>394.5293119943663</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>31.95</v>
+        <v>25.55</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>49.25174575821848</v>
+        <v>53.13600532990019</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>15.88143548167537</v>
+        <v>9.98300658508543</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.3936055547100562</v>
+        <v>1.245544017358958</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.2073942254572092</v>
+        <v>0.6626598462070222</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6861</v>
+        <v>7823</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>349.4732056392173</v>
+        <v>391.0802875326286</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>183</v>
+        <v>83</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>37.34721152430301</v>
+        <v>47.44145936649989</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>23.01887413747618</v>
+        <v>21.35354095074747</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.700661562679507</v>
+        <v>0.384836320499791</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>1.233465682144899</v>
+        <v>-0.0640491053983417</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>8028</v>
+        <v>6931</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>347.8217224060563</v>
+        <v>391.0483452888826</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>239</v>
+        <v>41</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>40.89671741142821</v>
+        <v>52.49705736848048</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>21.52574929786504</v>
+        <v>26.39830811276025</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5031811359946147</v>
+        <v>0.4811506373813949</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.7073386081506694</v>
+        <v>-0.1023227276510604</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6890</v>
+        <v>6965</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>338.2542498595504</v>
+        <v>383.8039266829329</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>169.5</v>
+        <v>73.8</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>48.72943869562062</v>
+        <v>39.4554331804141</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15.11828549261241</v>
+        <v>37.10149798248407</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.7904745143222</v>
+        <v>0.4990695581588331</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>1.278749394943231</v>
+        <v>0.0027468197377589</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7769</v>
+        <v>7747</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>337.4755334582261</v>
+        <v>383.7207206889119</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>5980</v>
+        <v>114.5</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>44.40543381190325</v>
+        <v>52.28716937920595</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>10.29386201158694</v>
+        <v>7.738805898866433</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.6716804827323589</v>
+        <v>0.5987004323292336</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-56.41576496484498</v>
+        <v>1.533853087185285</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>7734</v>
+        <v>7805</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>333.6232399686249</v>
+        <v>380.6312236449497</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>2890</v>
+        <v>508</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>46.53628885259745</v>
+        <v>30.86769555224934</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>17.19798629479317</v>
+        <v>37.70693087859446</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.7238124896919731</v>
+        <v>0.3052466258249975</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>-13.43059311922845</v>
+        <v>-10.25911596617494</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6971</v>
+        <v>7402</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>330.1292677105622</v>
+        <v>379.7795465164086</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>26.1</v>
+        <v>104.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>48.85307251514061</v>
+        <v>45.00936179078612</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>15.61133274078483</v>
+        <v>19.37698361208553</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4395341734500113</v>
+        <v>0.2839218473967748</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0549144772869834</v>
+        <v>-0.4155022187000715</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6919</v>
+        <v>7842</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>328.8379986884134</v>
+        <v>379.6098523560556</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>86.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>32.89588019542936</v>
+        <v>52.17736566192975</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>20.32793871777593</v>
+        <v>16.99644004378623</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.7837998688413385</v>
+        <v>0.2475735057081269</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-2.491171938503444</v>
+        <v>-0.3664131891293101</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>7610</v>
+        <v>6910</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>327.8400491477936</v>
+        <v>373.6253930345202</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>1820</v>
+        <v>24.75</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>55.46601201389821</v>
+        <v>48.24904522491863</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>12.41334240468793</v>
+        <v>20.53989889123936</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.6750722681083622</v>
+        <v>0.8131336106056668</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>18.64057021171394</v>
+        <v>0.1079479552682782</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8034</v>
+        <v>8040</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>327.3413637770018</v>
+        <v>372.375018516868</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>19.45</v>
+        <v>75</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>49.7349472183096</v>
+        <v>50.72245769299805</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>25.89212061021956</v>
+        <v>17.74884159053389</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.6557265418922296</v>
+        <v>2.178249548662097</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.1507130855066271</v>
+        <v>1.196460415890313</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6994</v>
+        <v>7820</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>326.3529453072314</v>
+        <v>369.1871962403344</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>35.2</v>
+        <v>118</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>37.84258507114747</v>
+        <v>51.04014997969454</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>28.10109130135626</v>
+        <v>17.36585712426885</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.9523016077320916</v>
+        <v>2.021117603816445</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.3058752965017448</v>
+        <v>-0.4054582928240635</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6916</v>
+        <v>6863</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>324.4184158452994</v>
+        <v>363.6216242821312</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>18.7</v>
+        <v>104.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>50.32579267984125</v>
+        <v>37.33017922015448</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>8.421526740634274</v>
+        <v>16.41709103528386</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.8810027689632582</v>
+        <v>0.4657062153519374</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0406695324011989</v>
+        <v>-1.200410795714367</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6854</v>
+        <v>6957</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>321.9344592231602</v>
+        <v>363.5223086752743</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>92.8</v>
+        <v>219.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45.60685637220763</v>
+        <v>51.34309114320195</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>20.15794621807569</v>
+        <v>13.83856068602041</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.406490578488159</v>
+        <v>0.7229410612273673</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>1.068280013875078</v>
+        <v>-0.0724933825870139</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>7732</v>
+        <v>6877</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>320.5214950342758</v>
+        <v>359.7024639874854</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>33.55</v>
+        <v>110.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>45.28482801071088</v>
+        <v>37.7465403704039</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>6.677327156126225</v>
+        <v>22.39606345841139</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.1403109993300149</v>
+        <v>0.6390365203270036</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.1465109622684406</v>
+        <v>-0.4747157700758846</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>7799</v>
+        <v>6951</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>319.6233828675082</v>
+        <v>359.6187154235273</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>370</v>
+        <v>71</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>51.1049034601842</v>
+        <v>38.79163117188234</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>13.42477987443606</v>
+        <v>23.75265983387593</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.230908984612191</v>
+        <v>2.49452417335253</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>1.185544839623344</v>
+        <v>0.1006438858429181</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7704</v>
+        <v>6890</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>315.2586495060369</v>
+        <v>358.2542498595524</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>59.6</v>
+        <v>169.5</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>42.04219910432204</v>
+        <v>48.72943875275979</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>16.53192773897744</v>
+        <v>15.11828554474212</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.7012815861757498</v>
+        <v>1.7904745143222</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.5311143490514049</v>
+        <v>1.278749393321486</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6862</v>
+        <v>8028</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>314.7438003617449</v>
+        <v>347.8217224060567</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>140</v>
+        <v>239</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45.18060533256864</v>
+        <v>40.89671745386843</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>13.66863653289428</v>
+        <v>21.52574932375891</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.265163212810998</v>
+        <v>0.5031811359946147</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>1.119942056947913</v>
+        <v>0.7073386074828996</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>7780</v>
+        <v>7803</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>312.7073091758221</v>
+        <v>343.6351338529167</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>16.7</v>
+        <v>19.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>44.12320029834648</v>
+        <v>45.76103313407154</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>16.817683255847</v>
+        <v>11.76184775738393</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.7757530566864309</v>
+        <v>0.4461696336947307</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0236785741164889</v>
+        <v>0.09365541845861131</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6928</v>
+        <v>7821</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>309.5811678942285</v>
+        <v>339.0251658356116</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>48.5</v>
+        <v>39.55</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>49.62300754957209</v>
+        <v>48.26809024626562</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>13.05450768276758</v>
+        <v>12.14428899027767</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.7419145607072704</v>
+        <v>0.2707922093893103</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.1423870364255268</v>
+        <v>0.1325900264704342</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6908</v>
+        <v>7734</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>307.7246661242642</v>
+        <v>333.6232399686245</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>30.1</v>
+        <v>2890</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>32.04584697159611</v>
+        <v>46.53628886266081</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>32.46986331285245</v>
+        <v>17.19798629853228</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>2.175538576576189</v>
+        <v>0.7238124896919731</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.082080522347431</v>
+        <v>-13.43059312113628</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7855</v>
+        <v>6971</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>298.8676084869969</v>
+        <v>330.1292677105622</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>42.75</v>
+        <v>26.1</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,16 +4951,16 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>17.80758267521959</v>
+        <v>48.853072948832</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>50.6962449920645</v>
+        <v>15.61133276058757</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.2899570422745821</v>
+        <v>0.4395341734500113</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>1.608708396311524</v>
+        <v>0.0549144773156005</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8033</v>
+        <v>6919</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>293.2618398388451</v>
+        <v>328.8379986884134</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>176</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>45.2966103535141</v>
+        <v>32.8958962375219</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>12.34245056190637</v>
+        <v>20.32795959412102</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3132032473112415</v>
+        <v>0.7837998688413385</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-1.415608168482447</v>
+        <v>-2.4911722416908</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6899</v>
+        <v>8034</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>285.9168433172291</v>
+        <v>327.3413637770016</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>50</v>
+        <v>19.45</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>41.24711049903028</v>
+        <v>49.73494725820121</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>20.18697524851859</v>
+        <v>25.89212062652247</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.3404197375363823</v>
+        <v>0.6557265418922296</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.1366533355844882</v>
+        <v>0.1507130854970859</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>8024</v>
+        <v>7732</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>285.2626447242607</v>
+        <v>320.5214950342758</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>12.9</v>
+        <v>33.55</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>34.82051999248058</v>
+        <v>45.28483351747847</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>14.4198765639294</v>
+        <v>6.677329751106744</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.4288968458525645</v>
+        <v>0.1403109993300149</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0115996898512154</v>
+        <v>-0.1465109698525252</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7721</v>
+        <v>7799</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>285.2535410459928</v>
+        <v>319.6233828675082</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>60.9</v>
+        <v>370</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>43.33639307919049</v>
+        <v>51.10490357363353</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>14.34150658227255</v>
+        <v>13.42477986612642</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.6352258708211707</v>
+        <v>1.230908984612191</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.092855874810336</v>
+        <v>1.185544836570674</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>7722</v>
+        <v>7704</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>282.8807652430273</v>
+        <v>315.2586495060369</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>280</v>
+        <v>59.6</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>46.80498246025854</v>
+        <v>42.04219915861415</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>10.98505068948963</v>
+        <v>16.53192773472264</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.5910821352739245</v>
+        <v>0.7012815861757498</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.1737072567249833</v>
+        <v>-0.5311143490132398</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>7818</v>
+        <v>6862</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>282.8393856674074</v>
+        <v>314.7438003617449</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>60.7</v>
+        <v>140</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>34.11658290822497</v>
+        <v>45.18060542688036</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>18.56003950344342</v>
+        <v>13.6686366176482</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5841675594339006</v>
+        <v>1.265163212810998</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.0483180912403062</v>
+        <v>1.119942055993954</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6901</v>
+        <v>8033</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>277.1521712450563</v>
+        <v>308.2618398388452</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>14.95</v>
+        <v>176</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>36.65827110122084</v>
+        <v>45.29661036144465</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>12.68562602880546</v>
+        <v>12.34245055663276</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.6183074966392861</v>
+        <v>0.3132032473112415</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-0.1705576912086617</v>
+        <v>-1.415608168539688</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6902</v>
+        <v>6988</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>273.681852064219</v>
+        <v>303.5643398729789</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>125</v>
+        <v>11.85</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>46.77792256165655</v>
+        <v>49.28173266068385</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>11.5332727940359</v>
+        <v>6.564672818970044</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.4034943270305706</v>
+        <v>0.5154431935210853</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.4203317531276367</v>
+        <v>-0.0003772604770171</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, williams_r_recovery, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>7747</v>
+        <v>7760</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>268.720720688912</v>
+        <v>301.4080126290069</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>114.5</v>
+        <v>33.2</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>52.28716934804071</v>
+        <v>48.27195122133628</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>7.738805931887596</v>
+        <v>7.17274134874452</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.5987004323292336</v>
+        <v>0.8957969119170421</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>1.533853088234648</v>
+        <v>0.05728775365687</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6910</v>
+        <v>6899</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>258.625393034551</v>
+        <v>285.9168433172291</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>24.75</v>
+        <v>50</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>48.24904519772277</v>
+        <v>41.24711059694737</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>20.53989890335161</v>
+        <v>20.18697532665329</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8131336106056668</v>
+        <v>0.3404197375363823</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>0.1079479553064377</v>
+        <v>0.136653335479551</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6934</v>
+        <v>8024</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>256.5121828331712</v>
+        <v>285.2626447242607</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>72.59999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>45.81873170302661</v>
+        <v>34.82051999248058</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>13.65383368054492</v>
+        <v>14.4198765508499</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>1.455364257651857</v>
+        <v>0.4288968458525645</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.1210664921043581</v>
+        <v>0.0115996898512154</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6997</v>
+        <v>7722</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>252.3765137038488</v>
+        <v>282.8807652430274</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>38.37176116318616</v>
+        <v>46.80498236035835</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>8.72618016605427</v>
+        <v>10.98505090637814</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.1263157894736842</v>
+        <v>0.5910821352739245</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-3.144504504799403</v>
+        <v>0.1737072599685412</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>7791</v>
+        <v>7818</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>251.4903864079561</v>
+        <v>282.8393856674074</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>55</v>
+        <v>60.7</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>20.89464182947376</v>
+        <v>34.11658309350864</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>38.69442530019422</v>
+        <v>18.56003940357026</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.8559188613166829</v>
+        <v>0.5841675594339006</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>-0.0266186945866553</v>
+        <v>0.0483180907633185</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>7770</v>
+        <v>6901</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>250.541396340617</v>
+        <v>277.1521712450563</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>35</v>
+        <v>14.95</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>47.37909250394015</v>
+        <v>36.65827108622594</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>5.757742310367389</v>
+        <v>12.68562608058417</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.721569276609833</v>
+        <v>0.6183074966392861</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1404995648253745</v>
+        <v>-0.1705576911895815</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>8038</v>
+        <v>6902</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>245.0278906386525</v>
+        <v>273.681852064219</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>31.9</v>
+        <v>125</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>46.67775572966136</v>
+        <v>46.77792261449908</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>20.64754038547956</v>
+        <v>11.5332728058751</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.8205425911513157</v>
+        <v>0.4034943270305706</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>1</v>
@@ -5764,11 +5764,11 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.3144110116478988</v>
+        <v>-0.4203317535092257</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -5785,7 +5785,7 @@
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>243.550662849133</v>
+        <v>263.550662849133</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>17.35</v>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45.93361053072358</v>
+        <v>45.93361059514769</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>14.85124218870695</v>
+        <v>14.85124218651711</v>
       </c>
       <c r="J101" s="2" t="n">
         <v>0.7474539114698725</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5827,21 +5827,21 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6914</v>
+        <v>7547</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>241.3364575547389</v>
+        <v>262.3953842431202</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>121</v>
+        <v>50.8</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>19.95974067115753</v>
+        <v>45.01065898231253</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>33.66169649138376</v>
+        <v>11.10501921104114</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.7566463573138937</v>
+        <v>0.8719346049046321</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-2.272217847971509</v>
+        <v>-0.0423836823302292</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>8040</v>
+        <v>6934</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>232.375018516868</v>
+        <v>256.5121828331712</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>75</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>50.72245770183591</v>
+        <v>45.81873170302661</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>17.74884149342554</v>
+        <v>13.65383367923472</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>2.178249548662097</v>
+        <v>1.455364257651857</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>1.196460415871236</v>
+        <v>0.1210664921043581</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>7786</v>
+        <v>6997</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>231.1303764710078</v>
+        <v>252.3765137038488</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>116.5</v>
+        <v>0</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>35.81492131115905</v>
+        <v>38.37176117773961</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>15.49030632572496</v>
+        <v>8.726180173257253</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.4124648245617333</v>
+        <v>0.1263157894736842</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.5501261318481978</v>
+        <v>-3.144504505085594</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>7765</v>
+        <v>7791</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>231.0840592814147</v>
+        <v>251.4903864079561</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>221.5</v>
+        <v>55</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>41.28599768118216</v>
+        <v>20.89464189502391</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>23.7775382624075</v>
+        <v>38.69442536760437</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.156854971205897</v>
+        <v>0.8559188613166829</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.1548999241808994</v>
+        <v>-0.0266186945675701</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>7839</v>
+        <v>7770</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>230.2428141713433</v>
+        <v>250.541396340617</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>43.95</v>
+        <v>35</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>38.75316922152565</v>
+        <v>47.37909242751365</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>34.48200795367458</v>
+        <v>5.757742231450321</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.2345483917309964</v>
+        <v>1.721569276609833</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,11 +6082,11 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.0638081395230171</v>
+        <v>-0.1404995645200998</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>229.2244826475218</v>
+        <v>249.224482647522</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>75.3</v>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>44.3606578602185</v>
+        <v>44.36065771930706</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>8.717311664455604</v>
+        <v>8.717311667792092</v>
       </c>
       <c r="J107" s="2" t="n">
         <v>0.3333911923511063</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>-0.1156510850776799</v>
+        <v>-0.1156510847915071</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>7803</v>
+        <v>8038</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>228.6351338529168</v>
+        <v>245.0278906386526</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>19.5</v>
+        <v>31.9</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,16 +6170,16 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>45.76103318949469</v>
+        <v>46.6777559330316</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>11.76184774130223</v>
+        <v>20.6475403097978</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.4461696336947307</v>
+        <v>0.8205425911513157</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.09365541842045259</v>
+        <v>0.3144110115525027</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6955</v>
+        <v>6914</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>228.0734907557405</v>
+        <v>241.3364575547389</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>46.5810549009176</v>
+        <v>19.95974067627158</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>6.848013449843142</v>
+        <v>33.6616965112745</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.327426915583884</v>
+        <v>0.7566463573138937</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-1.556139710980166</v>
+        <v>-2.272217848257719</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6909</v>
+        <v>7786</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>225.6593043519573</v>
+        <v>231.1303764710074</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>40.7</v>
+        <v>116.5</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>46.04046386323402</v>
+        <v>35.8149211271047</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>16.03585395852318</v>
+        <v>15.49030626733366</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.7986899442116073</v>
+        <v>0.4124648245617333</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>0.2925278382446663</v>
+        <v>-0.550126132038987</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>7821</v>
+        <v>7765</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>224.0251658356116</v>
+        <v>231.0840592814147</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>39.55</v>
+        <v>221.5</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>48.26808998579325</v>
+        <v>41.28599804552972</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>12.14428898254638</v>
+        <v>23.77753842538498</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.2707922093893103</v>
+        <v>1.156854971205897</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>0.1325900264704342</v>
+        <v>-0.1548999257072605</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6947</v>
+        <v>7839</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>215.805204520222</v>
+        <v>230.2428141713433</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>69.8</v>
+        <v>43.95</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>39.65300310825075</v>
+        <v>38.75316836295703</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>11.00697024572199</v>
+        <v>34.48200792500979</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.923166395489642</v>
+        <v>0.2345483917309964</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.1608014264012469</v>
+        <v>-0.06380813984736711</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8032</v>
+        <v>6955</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>213.1595673079718</v>
+        <v>228.0734907557405</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>35.7</v>
+        <v>100</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>42.39069974434333</v>
+        <v>46.58105489616693</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>19.89757170545612</v>
+        <v>6.848013347603365</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.5696535244922342</v>
+        <v>0.327426915583884</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0821356615547077</v>
+        <v>-1.556139710884775</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6967</v>
+        <v>6909</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>211.3008605398604</v>
+        <v>225.6593043519573</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>69.2</v>
+        <v>40.7</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>41.83081080300763</v>
+        <v>46.04046378498762</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>9.6831331708285</v>
+        <v>16.03585397567105</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.4406821859828209</v>
+        <v>0.7986899442116073</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.3602719215258129</v>
+        <v>0.2925278383209861</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>8011</v>
+        <v>6947</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>210.132194336226</v>
+        <v>215.805204520222</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>15.7</v>
+        <v>69.8</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>39.31399651238158</v>
+        <v>39.65300308188932</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>26.07746663859519</v>
+        <v>11.00697026423225</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.7364542635293092</v>
+        <v>0.923166395489642</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.0111776325701578</v>
+        <v>0.160801426782827</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>7740</v>
+        <v>8032</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>205.2861407694355</v>
+        <v>213.1595673079716</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>132</v>
+        <v>35.7</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>40.65741135802722</v>
+        <v>42.39069987833439</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>13.90147935521361</v>
+        <v>19.89757175257936</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.3512824869871185</v>
+        <v>0.5696535244922342</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,7 +6612,7 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.5834522606877393</v>
+        <v>0.08213566143069</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
@@ -6622,21 +6622,21 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>7705</v>
+        <v>6967</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>202.4170372108541</v>
+        <v>211.3008605398608</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>29.85</v>
+        <v>69.2</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>40.1989206655888</v>
+        <v>41.83080849012683</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>16.70125115558823</v>
+        <v>9.683131780851721</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.493930496995615</v>
+        <v>0.4406821859828209</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.09174598954407789</v>
+        <v>-0.3602719120623995</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6988</v>
+        <v>8011</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>188.5643398729788</v>
+        <v>210.1321943362259</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>11.85</v>
+        <v>15.7</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>49.28173255446134</v>
+        <v>39.31399665444965</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>6.564672818970043</v>
+        <v>26.07746668505277</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.5154431935210853</v>
+        <v>0.7364542635293092</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.000377260314842</v>
+        <v>0.0111776325606219</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, williams_r_recovery, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>7760</v>
+        <v>7740</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>186.4080126290069</v>
+        <v>205.2861407694354</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>33.2</v>
+        <v>132</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,16 +6753,16 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>48.27195122133628</v>
+        <v>40.65741134097556</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>7.172741347906612</v>
+        <v>13.90147938626796</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.8957969119170421</v>
+        <v>0.3512824869871185</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>0.05728775365687</v>
+        <v>-0.5834522607831261</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>7749</v>
+        <v>7705</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>175.8067663614908</v>
+        <v>202.4170372108538</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>368.5</v>
+        <v>29.85</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>52.09841523425572</v>
+        <v>40.19892051965322</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>16.44162896366197</v>
+        <v>16.70125123208427</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.7657427442528182</v>
+        <v>1.493930496995615</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>2.876201764824523</v>
+        <v>-0.0917459894677599</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>6873</v>
+        <v>7749</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>173.4136750781128</v>
+        <v>195.8067663614909</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>68.09999999999999</v>
+        <v>368.5</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>34.92685397726567</v>
+        <v>52.09841540044109</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>24.08484771933317</v>
+        <v>16.44162896368913</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.4122985321129628</v>
+        <v>0.7657427442528182</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>0.3511119080981699</v>
+        <v>2.876201761008634</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6925</v>
+        <v>7827</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>171.9210922011839</v>
+        <v>189.6639980869425</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>50</v>
+        <v>151</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,16 +6912,16 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>39.42291037942363</v>
+        <v>42.05701310558747</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>10.3007788283016</v>
+        <v>10.65606086304156</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.2904266505795418</v>
+        <v>0.5826725493162489</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.1822484574528717</v>
+        <v>-1.002652518712945</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>7827</v>
+        <v>6873</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>169.6639980869425</v>
+        <v>173.4136750781128</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>151</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>42.05701311862265</v>
+        <v>34.92685361538179</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>10.65606091892924</v>
+        <v>24.08484781716925</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.5826725493162489</v>
+        <v>0.4122985321129628</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,31 +6983,31 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-1.002652518712945</v>
+        <v>0.3511119089567409</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>7736</v>
+        <v>6925</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>164.3801663016471</v>
+        <v>171.9210922011839</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>69.40000000000001</v>
+        <v>50</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>46.80621905620153</v>
+        <v>39.42291023631896</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>13.33361456065768</v>
+        <v>10.30077871194941</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.3395585738539898</v>
+        <v>0.2904266505795418</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0186024215038053</v>
+        <v>0.1822484565943012</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>7753</v>
+        <v>7736</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>154.8969130016356</v>
+        <v>164.3801663016471</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>36.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>38.0623965567421</v>
+        <v>46.80621916881508</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>9.447398187550869</v>
+        <v>13.33361462169875</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.3310436149962757</v>
+        <v>0.3395585738539898</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>0.0264663085996256</v>
+        <v>0.0186024211794661</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>7547</v>
+        <v>7753</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>147.3953842430984</v>
+        <v>154.8969130016358</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>50.8</v>
+        <v>36.5</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>45.01065956261079</v>
+        <v>38.06239664036848</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>11.1050186709862</v>
+        <v>9.447398212415978</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.8719346049046321</v>
+        <v>0.3310436149962757</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,11 +7142,11 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>-0.0423836841427643</v>
+        <v>0.0264663087331895</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
@@ -7186,7 +7186,7 @@
         <v>0.1219127054822252</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L127" s="2" t="n">
         <v>0</v>
@@ -7230,7 +7230,7 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>41.37390042949671</v>
+        <v>41.37390030347555</v>
       </c>
       <c r="I128" s="2" t="n">
         <v>13.83430762897185</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-0.0684311216645288</v>
+        <v>-0.0684311214737174</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
